--- a/output/full_scan/batch_seq0_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq0_2026-06-18.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -527,21 +527,21 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>8088</v>
+        <v>8081</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>品安</t>
+          <t>致新</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1030.926491319671</v>
+        <v>1377.141664426578</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>69.2</v>
+        <v>319</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
@@ -552,49 +552,49 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>65.84386517391394</v>
+        <v>70.35778808335658</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>25.30004880354642</v>
+        <v>27.33511858954004</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>2.290811009597169</v>
+        <v>2.814166442657826</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3901387786096872</v>
+        <v>2.247706925512622</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>8081</v>
+        <v>8088</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>致新</t>
+          <t>品安</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1007.123462626161</v>
+        <v>1230.926491319671</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>319</v>
+        <v>69.2</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>70.3577880888765</v>
+        <v>65.84386517689194</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>27.33511857892576</v>
+        <v>25.30004877410112</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>2.812346262616064</v>
+        <v>2.290811009597169</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>2.247706924844797</v>
+        <v>0.3901387784475139</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>8215</v>
+        <v>8091</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>翔名</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>958.5691125606586</v>
+        <v>1214.378210148017</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>31.15</v>
+        <v>281</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,13 +658,13 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>56.81011839223376</v>
+        <v>65.70155568043529</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>27.04284491046581</v>
+        <v>34.60272487905469</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.639649367515072</v>
+        <v>2.825772939097178</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>0.0326497431176056</v>
+        <v>-0.2599537860525256</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>8091</v>
+        <v>8996</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>翔名</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>939.3782101480168</v>
+        <v>1155.853310953276</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>281</v>
+        <v>1590</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>65.70155567160616</v>
+        <v>71.7455822256853</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>34.60272489170701</v>
+        <v>20.67855727497209</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.825772939097178</v>
+        <v>1.526273322996542</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>-0.2599537862433259</v>
+        <v>42.43304677907224</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8163</v>
+        <v>8086</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>827.1515826794953</v>
+        <v>1054.360297485652</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>44.95</v>
+        <v>166</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>71.74573518915933</v>
+        <v>57.71111548486585</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>49.79088881709517</v>
+        <v>21.56960171470994</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.171170220501482</v>
+        <v>1.164992444713737</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.08844939454975929</v>
+        <v>0.1422459219353504</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8121</v>
+        <v>8358</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>817.2621264178638</v>
+        <v>1041.009352392484</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>53.4</v>
+        <v>700</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>75.93609080610463</v>
+        <v>69.04403229048192</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46.70069254133021</v>
+        <v>23.06894061513817</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.544987984983442</v>
+        <v>0.7056367516551425</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.8737442588502251</v>
+        <v>2.076261091978374</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, bb_squeeze_breakout, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8996</v>
+        <v>8121</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>790.8533109532763</v>
+        <v>1037.262126417864</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1590</v>
+        <v>53.4</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>71.74558222732101</v>
+        <v>75.93609080874364</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>20.67855731749224</v>
+        <v>46.70069252349768</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.526273322996542</v>
+        <v>1.544987984983442</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>42.43304677802282</v>
+        <v>0.8737442589074651</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8086</v>
+        <v>8215</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>774.3602974856524</v>
+        <v>1033.569112560659</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>166</v>
+        <v>31.15</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57.71111541919742</v>
+        <v>56.81011835213402</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>21.56960171470994</v>
+        <v>27.04284492152312</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.164992444713737</v>
+        <v>1.639649367515072</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.1422459220307546</v>
+        <v>0.0326497432797794</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>9105</v>
+        <v>8162</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>泰金寶-DR</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>756.5526502021388</v>
+        <v>898.5046576435245</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>9.529999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>56.78910258320517</v>
+        <v>63.85196161387863</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>46.85799265011362</v>
+        <v>40.24633442339601</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.3627102978701191</v>
+        <v>1.567442051946094</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.1991679809065785</v>
+        <v>-0.4335849669893434</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8112</v>
+        <v>8163</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>732.4444267459938</v>
+        <v>897.1515826794953</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>98.2</v>
+        <v>44.95</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>61.75508232112568</v>
+        <v>71.74573519855514</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>25.86234049884659</v>
+        <v>49.79088880869254</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.421772935862368</v>
+        <v>1.171170220501482</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.5103956454588987</v>
+        <v>0.08844939460700189</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>8076</v>
+        <v>8261</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>富鼎</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>731.6368520244017</v>
+        <v>896.702351686249</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>25.75</v>
+        <v>215</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>51.69424157619022</v>
+        <v>70.77460366612414</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>22.4317479400567</v>
+        <v>38.10033705324225</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.5250873403966899</v>
+        <v>0.2754175112672038</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>-0.1767854191111162</v>
+        <v>2.14249691303282</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8926</v>
+        <v>8438</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>720.4604029481216</v>
+        <v>890.5228465530489</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>79</v>
+        <v>92.5</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>70.25998962755904</v>
+        <v>58.67902818406253</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>52.16270358114066</v>
+        <v>14.57775227466842</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.8690289882885064</v>
+        <v>2.959531275522715</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.1949277299399305</v>
+        <v>0.5272493879090294</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8072</v>
+        <v>8476</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>719.7429042208435</v>
+        <v>888.1208831555517</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>29.4</v>
+        <v>21.75</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.53291288479573</v>
+        <v>84.31001297108764</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>22.71628374643432</v>
+        <v>45.00316505244118</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.8253136942312305</v>
+        <v>2.912088315555169</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.0181312603543747</v>
+        <v>0.5541364431437922</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8105</v>
+        <v>8096</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>718.7211697479768</v>
+        <v>875.5250652683885</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>21.9</v>
+        <v>155.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>65.19188567018112</v>
+        <v>72.18532653945576</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>41.19884811391349</v>
+        <v>44.18588691588744</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7588550714363653</v>
+        <v>0.7203246007847947</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.0227908851035025</v>
+        <v>1.807926965731887</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8261</v>
+        <v>8071</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>富鼎</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>716.702351686249</v>
+        <v>815.3018019305124</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>215</v>
+        <v>29.4</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>70.77460366772166</v>
+        <v>72.67611105911736</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>38.10033709606233</v>
+        <v>44.8860879633117</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.2754175112672038</v>
+        <v>0.9847190895920004</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>2.142496912632176</v>
+        <v>0.7530224316757033</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8473</v>
+        <v>8926</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>715.1747735264522</v>
+        <v>795.4604029481216</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>57.93937361535146</v>
+        <v>70.25998962481813</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>37.58338584607165</v>
+        <v>52.1627035734376</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.3216518492864711</v>
+        <v>0.8690289882885064</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.7074883682110529</v>
+        <v>0.1949277299780902</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8162</v>
+        <v>8454</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>富邦媒</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>678.5046576435245</v>
+        <v>775.5899539744237</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>341</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>63.85196162329516</v>
+        <v>60.04521210663605</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>40.24633438137679</v>
+        <v>53.07203140060524</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.567442051946094</v>
+        <v>0.4129375977969646</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.4335849672087573</v>
+        <v>-3.73556959725768</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>8476</v>
+        <v>8048</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>德勝</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>678.1208831555517</v>
+        <v>757.6383202555471</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>21.75</v>
+        <v>66.3</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>84.3100130000925</v>
+        <v>56.52136123350153</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45.00316493037773</v>
+        <v>19.094625804493</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.912088315555169</v>
+        <v>0.5944091145213469</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.5541364430388547</v>
+        <v>0.3309040217859146</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>8096</v>
+        <v>9105</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>泰金寶-DR</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>675.5250652683885</v>
+        <v>756.5526502021388</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>155.5</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>72.18532652107436</v>
+        <v>56.78910258015827</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>44.18588683939685</v>
+        <v>46.85799258785438</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.7203246007847947</v>
+        <v>0.3627102978701191</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.807926965941753</v>
+        <v>-0.1991679808798678</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8070</v>
+        <v>8112</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>664.7017946632876</v>
+        <v>732.4444267459938</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>55</v>
+        <v>98.2</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>52.80344356558434</v>
+        <v>61.75508233411573</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>28.91457798421461</v>
+        <v>25.8623405089959</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.3794917228330856</v>
+        <v>0.421772935862368</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.6298633158374844</v>
+        <v>0.5103956454779883</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8390</v>
+        <v>8076</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>655.3455214206044</v>
+        <v>731.6368520244017</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>114</v>
+        <v>25.75</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>49.45085485903427</v>
+        <v>51.69424156179807</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>27.54129964987519</v>
+        <v>22.431747942232</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.8232000378977669</v>
+        <v>0.5250873403966899</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-1.924104158368309</v>
+        <v>-0.1767854190157202</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8438</v>
+        <v>8105</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>650.5228465530489</v>
+        <v>718.7211697479768</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>92.5</v>
+        <v>21.9</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>58.67902818643597</v>
+        <v>65.19188567018112</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>14.57775227819339</v>
+        <v>41.19884809914242</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.959531275522715</v>
+        <v>0.7588550714363653</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.5272493878899476</v>
+        <v>0.0227908851512006</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>9912</v>
+        <v>8104</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>645.4825753324391</v>
+        <v>710.187417986814</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>12.65</v>
+        <v>42.35</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>56.77164915348562</v>
+        <v>61.36984925690612</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>21.7726958744263</v>
+        <v>31.24790243999222</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.1482575332439052</v>
+        <v>1.43601893816944</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.0108650058216711</v>
+        <v>-0.061119653482994</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8050</v>
+        <v>8155</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>廣積</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>628.7800003462955</v>
+        <v>704.8409076963212</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>55.7</v>
+        <v>404.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>53.57349044680238</v>
+        <v>56.62878197545385</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>43.87614393999345</v>
+        <v>19.42216355662317</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.2739436714540413</v>
+        <v>0.7286666136586196</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-0.7818196978322467</v>
+        <v>2.389014179137372</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8488</v>
+        <v>8072</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>624.3576534660657</v>
+        <v>699.7429042208328</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>10.55</v>
+        <v>29.4</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>54.31968267248797</v>
+        <v>56.53291229429286</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>11.52070079983986</v>
+        <v>22.71628386793744</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4213806284477214</v>
+        <v>0.8253136942312305</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.0503701023674696</v>
+        <v>0.01813126120341</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8472</v>
+        <v>8473</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>623.7277693227371</v>
+        <v>695.1747735264522</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>85.5</v>
+        <v>50</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>56.09315928539793</v>
+        <v>57.93937361535146</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>28.48304232858862</v>
+        <v>37.58338584790121</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.0446880676429455</v>
+        <v>0.3216518492864711</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.4838855887222637</v>
+        <v>-0.7074883681156581</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8499</v>
+        <v>8488</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>621.5452454546102</v>
+        <v>694.3576534660657</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>304</v>
+        <v>10.55</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>55.34727824400827</v>
+        <v>54.31968271960501</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>14.779894763618</v>
+        <v>11.52070081506104</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4035730410363002</v>
+        <v>0.4213806284477214</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.2193070179586675</v>
+        <v>0.050370102272073</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8071</v>
+        <v>8499</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>615.3018019305124</v>
+        <v>691.5452454546102</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>29.4</v>
+        <v>304</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>72.67611106515</v>
+        <v>55.3472782183686</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>44.88608798042002</v>
+        <v>14.77989475140978</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.9847190895920004</v>
+        <v>0.4035730410363002</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.7530224316089242</v>
+        <v>0.2193070184356582</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>8383</v>
+        <v>9912</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>614.3378558329428</v>
+        <v>675.4825753324391</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>60.4</v>
+        <v>12.65</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>52.9068280945873</v>
+        <v>56.77164012606635</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15.85208666391401</v>
+        <v>21.77269587606584</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.5014785425891116</v>
+        <v>0.1482575332439052</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0001553528287235</v>
+        <v>0.0108650058121316</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8182</v>
+        <v>8064</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>東捷</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>613.2018474242929</v>
+        <v>670.3729581034032</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>51</v>
+        <v>156</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>58.7551005741056</v>
+        <v>60.43773054181896</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>28.27668791740705</v>
+        <v>36.25600804110526</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.3842023107047386</v>
+        <v>0.9098603786064656</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.162361523770826</v>
+        <v>-2.143456445377392</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8341</v>
+        <v>8131</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>609.6675098134273</v>
+        <v>669.5485995398493</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>58.95113393290296</v>
+        <v>60.21988201490265</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>27.58821508489241</v>
+        <v>16.13060111251273</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.541528718514066</v>
+        <v>0.7203650281217829</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.1033912333086977</v>
+        <v>0.5138690387225906</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8481</v>
+        <v>8390</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>598.332906863063</v>
+        <v>655.3455214206044</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>42.1</v>
+        <v>114</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>65.03013396479946</v>
+        <v>49.45085486065919</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>28.08286107095129</v>
+        <v>27.54129967618764</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.2287099038011074</v>
+        <v>0.8232000378977669</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1472931746808022</v>
+        <v>-1.924104158559102</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8049</v>
+        <v>8110</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>597.7001100879544</v>
+        <v>653.265532549499</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>27.7</v>
+        <v>59.2</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>62.15242187792689</v>
+        <v>57.57288957913019</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>25.21061426471751</v>
+        <v>18.18224149505588</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.784328461850071</v>
+        <v>0.5303929645891792</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.0676234060340976</v>
+        <v>-0.0187531580316782</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>9136</v>
+        <v>8050</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>廣積</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>596.3712942171848</v>
+        <v>648.7800003462955</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>16.7</v>
+        <v>55.7</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>68.12523700256952</v>
+        <v>53.57349040828037</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>53.27705616384912</v>
+        <v>43.87614420822859</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.3973425721198888</v>
+        <v>0.2739436714540413</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.0765001715781421</v>
+        <v>-0.7818196975079008</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8104</v>
+        <v>8109</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>博大</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>575.187417986814</v>
+        <v>645.5867867506764</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>42.35</v>
+        <v>123</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>61.36984926992316</v>
+        <v>56.638459764443</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>31.24790243643764</v>
+        <v>24.79535913142537</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.43601893816944</v>
+        <v>1.098256773799319</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-0.0611196536451674</v>
+        <v>-0.3862834970389164</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8097</v>
+        <v>8299</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>573.3863436447973</v>
+        <v>643.1243941611358</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>60.3</v>
+        <v>2530</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>61.94978161853431</v>
+        <v>55.41740483822416</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>26.30944129400334</v>
+        <v>15.53698698524009</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.104663461656446</v>
+        <v>1.078945723721084</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.0863948930294506</v>
+        <v>-21.54329255527637</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8048</v>
+        <v>8472</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>德勝</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>572.638320255547</v>
+        <v>623.7277693227371</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>66.3</v>
+        <v>85.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>56.52136121929877</v>
+        <v>56.09315923728956</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>19.09462580961792</v>
+        <v>28.48304235708011</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.5944091145213469</v>
+        <v>0.0446880676429455</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.3309040217382146</v>
+        <v>-0.4838855884646884</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8131</v>
+        <v>8383</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>569.5485995398493</v>
+        <v>614.3378558329428</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>60.4</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>60.21988201403603</v>
+        <v>52.90682818116999</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>16.13060112213119</v>
+        <v>15.85208672734539</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7203650281217829</v>
+        <v>0.5014785425891116</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.5138690387035059</v>
+        <v>0.0001553530481321</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8102</v>
+        <v>8182</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>564.053417284901</v>
+        <v>613.2018474242929</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>71.90000000000001</v>
+        <v>51</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>53.33748624138033</v>
+        <v>58.75510056928735</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>11.82006637782895</v>
+        <v>28.27668792031824</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.6692022450081282</v>
+        <v>0.3842023107047386</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>-0.7240692415222578</v>
+        <v>0.1623615238471472</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8110</v>
+        <v>8070</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>553.265532549499</v>
+        <v>609.7017946632876</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>59.2</v>
+        <v>55</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>57.57288958128</v>
+        <v>52.80344353169039</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>18.18224149505588</v>
+        <v>28.91457806866354</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5303929645891792</v>
+        <v>0.3794917228330856</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.0187531580603064</v>
+        <v>-0.6298633157039246</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>9907</v>
+        <v>8374</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>549.0165349655372</v>
+        <v>609.6788244174722</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>16.7</v>
+        <v>91</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>52.22988384335636</v>
+        <v>45.73648665440056</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21.66726414041177</v>
+        <v>19.24014436228724</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.34951109035133</v>
+        <v>0.2500614123425246</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>0.0804130730140652</v>
+        <v>-1.637911620008658</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8150</v>
+        <v>8049</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>548.8430734199715</v>
+        <v>597.7001100879544</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>104</v>
+        <v>27.7</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>60.01922406796404</v>
+        <v>62.15242187792689</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>27.3246381272385</v>
+        <v>25.21061429508586</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.24397190127226</v>
+        <v>0.784328461850071</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-0.37211653652012</v>
+        <v>0.0676234060627154</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>8210</v>
+        <v>9136</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>543.4915512369838</v>
+        <v>596.3712942171848</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1365</v>
+        <v>16.7</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>49.67300083430242</v>
+        <v>68.12523699545898</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>21.67862958879252</v>
+        <v>53.27705616779544</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6617032259710059</v>
+        <v>0.3973425721198888</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-17.7227485335835</v>
+        <v>-0.07650017157432649</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8289</v>
+        <v>8097</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>541.4865908102521</v>
+        <v>593.3863436447973</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>60.3</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>53.51604532942413</v>
+        <v>61.94978168801831</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>31.68555598950381</v>
+        <v>26.30944128685361</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.404624734127143</v>
+        <v>1.104663461656446</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-1.136857436787376</v>
+        <v>-0.08639489316300381</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8374</v>
+        <v>8069</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>539.6788244174724</v>
+        <v>582.1069887125407</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>91</v>
+        <v>204</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45.73648664592169</v>
+        <v>51.17272891764441</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>19.24014433365858</v>
+        <v>24.2564967733027</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.2500614123425246</v>
+        <v>1.279254106786174</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-1.637911620313941</v>
+        <v>-3.774413579516368</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>8109</v>
+        <v>9907</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>博大</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>535.5867867506763</v>
+        <v>579.0165349655372</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>123</v>
+        <v>16.7</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>56.63845975552528</v>
+        <v>52.22988369399163</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>24.79535917929955</v>
+        <v>21.66726423292999</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.098256773799319</v>
+        <v>2.34951109035133</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.3862834970579887</v>
+        <v>0.080413073099921</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8201</v>
+        <v>8341</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>519.3119614310266</v>
+        <v>569.6675098134273</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>13.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>52.29169891087445</v>
+        <v>58.95113406624979</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>22.90330870353725</v>
+        <v>27.58821510398439</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.3861157022261797</v>
+        <v>0.541528718514066</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.0158929567466764</v>
+        <v>0.1033912333850146</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8064</v>
+        <v>8102</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>東捷</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>500.3729581034031</v>
+        <v>564.053417284901</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>156</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>60.43773054362524</v>
+        <v>53.33748621701348</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>36.25600808930783</v>
+        <v>11.82006646968299</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.9098603786064656</v>
+        <v>0.6692022450081282</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-2.143456445282018</v>
+        <v>-0.7240692413123728</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8093</v>
+        <v>8481</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>保銳</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>496.4614583934694</v>
+        <v>558.332906863063</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>19.3</v>
+        <v>42.1</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>52.81173140699266</v>
+        <v>65.03013428144452</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>8.674957395091818</v>
+        <v>28.08286115400882</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.46580909010292</v>
+        <v>0.2287099038011074</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.411045079361697</v>
+        <v>0.1472931744900086</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>9906</v>
+        <v>8464</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>490.5188776804989</v>
+        <v>545.8962450110483</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>46.8</v>
+        <v>358</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,49 +3149,49 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>66.85193062953604</v>
+        <v>65.60310648095518</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>41.40916467474868</v>
+        <v>19.41685786728148</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.191740628696065</v>
+        <v>1.232676659989646</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M51" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.8050964843730153</v>
+        <v>4.441399040436155</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8277</v>
+        <v>8289</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>商丞</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>483.286255843012</v>
+        <v>541.4865908102521</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>9.550000000000001</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>52.14882591225888</v>
+        <v>53.51604533190066</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>32.15352321807622</v>
+        <v>31.68555592769697</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.9383892352688604</v>
+        <v>0.404624734127143</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.0971425532247818</v>
+        <v>-1.136857436777838</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8271</v>
+        <v>8210</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>477.5958194479641</v>
+        <v>538.4915512369838</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>211</v>
+        <v>1365</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45.63758887856774</v>
+        <v>49.67300081800688</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.06666725799814</v>
+        <v>21.67862955376237</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.4745126093154982</v>
+        <v>0.6617032259710059</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-3.291086553103923</v>
+        <v>-17.72274853072158</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>8299</v>
+        <v>9905</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>473.1213197895452</v>
+        <v>537.2249845343975</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2530</v>
+        <v>21.05</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>55.41740485096602</v>
+        <v>57.77401140328696</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>15.53698700026042</v>
+        <v>17.58795026071824</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.078696265864173</v>
+        <v>0.4720299394802166</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-21.54329255880586</v>
+        <v>0.0641032332594579</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8080</v>
+        <v>8150</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>470.6087851783257</v>
+        <v>508.8430734199715</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>28.8</v>
+        <v>104</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>56.45154474828797</v>
+        <v>60.01922406754734</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>43.37176858621142</v>
+        <v>27.32463813529739</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.7756517776826294</v>
+        <v>1.24397190127226</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>0.08915620162368749</v>
+        <v>-0.3721165364437979</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, cci_momentum</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>9905</v>
+        <v>8277</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>商丞</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>467.2249845343976</v>
+        <v>503.286255843012</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>21.05</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>57.77401140328696</v>
+        <v>52.1488259050955</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>17.58795019835933</v>
+        <v>32.15352321807622</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.4720299394802166</v>
+        <v>0.9383892352688604</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0641032332499195</v>
+        <v>-0.0971425532209651</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>9110</v>
+        <v>8093</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>保銳</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>463.7111404797045</v>
+        <v>496.4614583934695</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>3.4</v>
+        <v>19.3</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.3882730162877</v>
+        <v>52.81173141278106</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15.74909256205853</v>
+        <v>8.674957226959718</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2778971617596257</v>
+        <v>1.46580909010292</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.0104481036359067</v>
+        <v>0.4110450794107465</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>9103</v>
+        <v>8201</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>461.5604128376082</v>
+        <v>479.3119614310266</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>5.33</v>
+        <v>13.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>48.38557725352536</v>
+        <v>52.29169882303583</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>32.99696614565642</v>
+        <v>22.90330873716831</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3714204211342013</v>
+        <v>0.3861157022261797</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0644255513568134</v>
+        <v>-0.0158929566417384</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8155</v>
+        <v>8080</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>459.8409076963212</v>
+        <v>470.6087851783257</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>404.5</v>
+        <v>28.8</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>56.6287819833607</v>
+        <v>56.45154460523543</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>19.4221635669653</v>
+        <v>43.37176839127427</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7286666136586196</v>
+        <v>0.7756517776826294</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>2.389014178660386</v>
+        <v>0.0891562017286243</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>8464</v>
+        <v>9110</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>450.8962450110487</v>
+        <v>463.7111404797045</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>358</v>
+        <v>3.4</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>65.6031064462875</v>
+        <v>54.38827536821917</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>19.41685770102207</v>
+        <v>15.74909254953022</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.232676659989646</v>
+        <v>0.2778971617596257</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>4.441399038814391</v>
+        <v>-0.0104481036359067</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>8087</v>
+        <v>9930</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>448.7492886899026</v>
+        <v>462.3042774755675</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>33.1</v>
+        <v>70</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>44.12416581455841</v>
+        <v>58.46715913726457</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>20.25952175730305</v>
+        <v>12.44044185185889</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.625635842633647</v>
+        <v>1.169870024537477</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.23235002093175</v>
+        <v>0.1533665392640847</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>9930</v>
+        <v>9103</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>442.3042774755675</v>
+        <v>461.5604128376081</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>70</v>
+        <v>5.33</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>58.46715903469917</v>
+        <v>48.38557725352536</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>12.44044183528875</v>
+        <v>32.99696616510596</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.169870024537477</v>
+        <v>0.3714204211342013</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.1533665392640847</v>
+        <v>-0.0644255513587223</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>8069</v>
+        <v>9906</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>397.1069887125407</v>
+        <v>450.5188776804988</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>204</v>
+        <v>46.8</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>51.17272891380384</v>
+        <v>66.85193063403479</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>24.25649662067359</v>
+        <v>41.40916464164901</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.279254106786174</v>
+        <v>2.191740628696065</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-3.774413579230166</v>
+        <v>0.8050964845447268</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>9910</v>
+        <v>8087</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>382.3920881368412</v>
+        <v>448.7492886899026</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>33.1</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>43.81768795247864</v>
+        <v>44.12416580371332</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>25.52107577593717</v>
+        <v>20.25952175859864</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.5864932777212982</v>
+        <v>0.625635842633647</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.8750232238591815</v>
+        <v>-0.23235002093175</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8101</v>
+        <v>8271</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>374.0027008741864</v>
+        <v>437.5958194479642</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>14.45</v>
+        <v>211</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>49.49949455314339</v>
+        <v>45.63758887204092</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15.59200881283793</v>
+        <v>21.06666723098323</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.2949415259518292</v>
+        <v>0.4745126093154982</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-0.154532186377353</v>
+        <v>-3.291086552932189</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>8068</v>
+        <v>9910</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>372.7506539284531</v>
+        <v>417.3920881368412</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>19.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>41.29453020262251</v>
+        <v>43.81768797397033</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>23.74262920044136</v>
+        <v>25.52107577369674</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.92859899366724</v>
+        <v>0.5864932777212982</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0490773108658718</v>
+        <v>-0.8750232240499938</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8067</v>
+        <v>8101</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>368.6342266126773</v>
+        <v>404.0027008741864</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>12.8</v>
+        <v>14.45</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>50.82317177573691</v>
+        <v>49.4994945389498</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>6.61555087810469</v>
+        <v>15.59200879353696</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6358510214776845</v>
+        <v>0.2949415259518292</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.1641368223061953</v>
+        <v>-0.154532186358273</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4025,21 +4025,21 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8455</v>
+        <v>8176</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>366.535021036419</v>
+        <v>402.5398038362733</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>31.1</v>
+        <v>10.15</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45.40372607345672</v>
+        <v>46.88977771623104</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>23.05434325953021</v>
+        <v>9.021694678918497</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.1955059621391223</v>
+        <v>1.245876290072259</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-1.091089417168995</v>
+        <v>0.0044568676957452</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8054</v>
+        <v>8068</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>354.9125939734548</v>
+        <v>392.7506539284531</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>103.5</v>
+        <v>19.2</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.41739106991384</v>
+        <v>41.29453027294502</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10.66746601501775</v>
+        <v>23.74262922136042</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.8530098015440434</v>
+        <v>0.92859899366724</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.010904773695312</v>
+        <v>0.0490773109040287</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8477</v>
+        <v>8411</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>352.5606681884926</v>
+        <v>389.4175481065753</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>17.2</v>
+        <v>12.15</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.1320300339943</v>
+        <v>49.91804091976477</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>28.20344556396455</v>
+        <v>33.77147256005432</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.35685727326736</v>
+        <v>1.687056878824431</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.4065303894161066</v>
+        <v>0.01054904063613</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>9908</v>
+        <v>9904</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>351.2236966339877</v>
+        <v>387.6726002816658</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>29.55</v>
+        <v>26.15</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>54.89931306089676</v>
+        <v>48.14128497683792</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>15.44949200240722</v>
+        <v>17.83460861250862</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.359640313823974</v>
+        <v>2.106641881407974</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0529898624546575</v>
+        <v>0.058975238870303</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8422</v>
+        <v>8442</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>347.6263480424821</v>
+        <v>378.0301115522864</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>28.1</v>
+        <v>40.3</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>49.7386024874543</v>
+        <v>35.98476082437912</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.26696392722913</v>
+        <v>22.1417566843635</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5636579756162637</v>
+        <v>0.6260510736652275</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.0565524571176091</v>
+        <v>0.4217338447914149</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8103</v>
+        <v>8054</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>347.0146493282012</v>
+        <v>374.9125939734548</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>97.09999999999999</v>
+        <v>103.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>44.18854532951462</v>
+        <v>51.41739109336533</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>20.45178678267854</v>
+        <v>10.66746599368151</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5409881363708172</v>
+        <v>0.8530098015440434</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,11 +4333,11 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.7162891855074536</v>
+        <v>-0.0109047733709579</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>344.233634195929</v>
+        <v>374.233634195929</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>212</v>
@@ -4368,10 +4368,10 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.86859048237448</v>
+        <v>45.86859040910159</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>27.715188442454</v>
+        <v>27.71518865929537</v>
       </c>
       <c r="J74" s="2" t="n">
         <v>0.4735362483682783</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-4.299485126725925</v>
+        <v>-4.299485125008794</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8074</v>
+        <v>8477</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>339.8744013306601</v>
+        <v>372.5606681884926</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>73.90000000000001</v>
+        <v>17.2</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,16 +4421,16 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>49.44624213035464</v>
+        <v>49.13203001979202</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>10.79600425622519</v>
+        <v>28.20344555008747</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.6524551145598754</v>
+        <v>0.35685727326736</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.096933758550324</v>
+        <v>-0.4065303894924257</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8227</v>
+        <v>8067</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>337.4274005798313</v>
+        <v>368.6342266126773</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>184.5</v>
+        <v>12.8</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>46.33647505976426</v>
+        <v>50.82317182677548</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>24.41225790532808</v>
+        <v>6.61555089611803</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4795257708521274</v>
+        <v>0.6358510214776845</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-4.061197611301567</v>
+        <v>-0.1641368224779111</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8089</v>
+        <v>8455</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>334.0010156160532</v>
+        <v>366.535021036419</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>21.15</v>
+        <v>31.1</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>51.64787503872545</v>
+        <v>45.40372605236342</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>33.79497211613785</v>
+        <v>23.05434328144319</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.99562590604665</v>
+        <v>0.1955059621391223</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1105617843138771</v>
+        <v>-1.091089417054512</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>9904</v>
+        <v>8431</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>332.1579839798047</v>
+        <v>355.3131014945473</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>26.15</v>
+        <v>57.6</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>48.14128496653766</v>
+        <v>54.27990389585754</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>17.83460857740994</v>
+        <v>16.80451562805866</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>2.017575395334711</v>
+        <v>1.19642007569765</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.0589752388512224</v>
+        <v>0.8006526449964846</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>8411</v>
+        <v>9902</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>319.4175481065753</v>
+        <v>352.811360768634</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>12.15</v>
+        <v>13.7</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>49.91804079431053</v>
+        <v>44.25725224951844</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>33.77147229386302</v>
+        <v>13.84569900861393</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.687056878824431</v>
+        <v>0.5057807995197909</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0105490406647487</v>
+        <v>-5.747257940474926e-06</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>8466</v>
+        <v>9908</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>312.8717668937186</v>
+        <v>351.2236966339877</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>15.55</v>
+        <v>29.55</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45.87086472891477</v>
+        <v>54.89931306089676</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>21.00218207082884</v>
+        <v>15.44949202565718</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.586492457580184</v>
+        <v>1.359640313823974</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0244693463115465</v>
+        <v>0.0529898624164991</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8442</v>
+        <v>8487</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>308.0301115522863</v>
+        <v>348.0886907801635</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>40.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>35.98476065000904</v>
+        <v>45.69987712678162</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>22.14175658090218</v>
+        <v>17.57347580463314</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.6260510736652275</v>
+        <v>0.2900147090196607</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>0.4217338445815413</v>
+        <v>-0.2309925473627782</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8234</v>
+        <v>8466</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>304.7133424084643</v>
+        <v>342.8717668937186</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>63.6</v>
+        <v>15.55</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>43.30283791847399</v>
+        <v>45.87086468382787</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>18.06138793203833</v>
+        <v>21.00218212608815</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.3231887694475174</v>
+        <v>0.586492457580184</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.6990391740476234</v>
+        <v>0.0244693464355625</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8429</v>
+        <v>8240</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>297.044486780294</v>
+        <v>342.3304375492121</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>6.51</v>
+        <v>56.9</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>49.23215612436684</v>
+        <v>41.06026707528156</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>26.60722660011366</v>
+        <v>17.6570474420099</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.380266615582537</v>
+        <v>0.3784004600914926</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0180581745643384</v>
+        <v>-0.4066624414126591</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8147</v>
+        <v>8074</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>294.7928650992018</v>
+        <v>339.8744013306601</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>146.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>39.8738992649724</v>
+        <v>49.44624212724676</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>21.57334456721795</v>
+        <v>10.79600427039511</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4033979836180008</v>
+        <v>0.6524551145598754</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-2.172759523125663</v>
+        <v>0.09693375857894999</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8176</v>
+        <v>8227</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>292.5398038362732</v>
+        <v>337.4274005798313</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>10.15</v>
+        <v>184.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46.88977798037127</v>
+        <v>46.33647509632365</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>9.021694674438136</v>
+        <v>24.41225788821432</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.245876290072259</v>
+        <v>0.4795257708521274</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.0044568675812705</v>
+        <v>-4.061197610538376</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8462</v>
+        <v>8089</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>285.9832095376831</v>
+        <v>334.0010156160555</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>139</v>
+        <v>21.15</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>42.51033616210383</v>
+        <v>51.64787532633137</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15.82974212846544</v>
+        <v>33.79497216679643</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.583061511248226</v>
+        <v>0.99562590604665</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.3308498861797418</v>
+        <v>0.1105617847145457</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8443</v>
+        <v>8111</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>266.7481694139776</v>
+        <v>330.6251297313991</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>11.4</v>
+        <v>56.2</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>48.28717672887021</v>
+        <v>37.31698985574555</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>56.43766506437439</v>
+        <v>27.19021227969117</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4656928902496394</v>
+        <v>0.7916411375919936</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.0305161088253596</v>
+        <v>-0.5533431235268038</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8111</v>
+        <v>8103</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>255.625129731399</v>
+        <v>327.0146493282012</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>56.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>37.31698971780743</v>
+        <v>44.18854536222097</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>27.19021230447475</v>
+        <v>20.4517868018715</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.7916411375919936</v>
+        <v>0.5409881363708172</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.5533431236603596</v>
+        <v>-0.7162891852622097</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8932</v>
+        <v>8429</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>251.1965771959167</v>
+        <v>317.044486780294</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>100</v>
+        <v>6.51</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>50.07671000947165</v>
+        <v>49.23215618114228</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15.78666147514223</v>
+        <v>26.60722660423146</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5416365423366842</v>
+        <v>1.380266615582537</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.2785236685248771</v>
+        <v>0.0180581745643384</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>9955</v>
+        <v>8422</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>249.3905025040084</v>
+        <v>307.6263480424821</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>26.95</v>
+        <v>28.1</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>41.56393136462542</v>
+        <v>49.7386024874543</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>22.08637765528348</v>
+        <v>16.26696395599885</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.8478093000344159</v>
+        <v>0.5636579756162637</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>-0.0069721953605607</v>
+        <v>0.0565524569541111</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8423</v>
+        <v>8234</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>247.9677165388879</v>
+        <v>304.7133424084689</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>17.75</v>
+        <v>63.6</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>47.42774801033885</v>
+        <v>43.30283782207498</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>12.99136027841185</v>
+        <v>18.06138796917998</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.585501965893761</v>
+        <v>0.3231887694475174</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0138510445177802</v>
+        <v>-0.6990391735133873</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8183</v>
+        <v>8443</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>247.8992485706265</v>
+        <v>296.7481694139776</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>32.55</v>
+        <v>11.4</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>51.57100204335151</v>
+        <v>48.28717664246225</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>13.67037260251163</v>
+        <v>56.43766512446177</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.5956788085759926</v>
+        <v>0.4656928902496394</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.1811238873586245</v>
+        <v>0.0305161088348983</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8940</v>
+        <v>8147</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>247.5093482338217</v>
+        <v>294.7928650992018</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>17</v>
+        <v>146.5</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>52.4229652853321</v>
+        <v>39.87389930504136</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>12.85198969691587</v>
+        <v>21.57334451226114</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.7557164579987778</v>
+        <v>0.4033979836180008</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,11 +5393,11 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0676787588087749</v>
+        <v>-2.172759522725013</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>242.7858263219995</v>
+        <v>272.7858263219994</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>151</v>
@@ -5428,10 +5428,10 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>41.65355117367157</v>
+        <v>41.65355115099919</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.53001858121348</v>
+        <v>16.53001859418741</v>
       </c>
       <c r="J94" s="2" t="n">
         <v>0.7646322489312642</v>
@@ -5446,7 +5446,7 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.3240151446673727</v>
+        <v>-0.3240151441903944</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
@@ -5456,21 +5456,21 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8487</v>
+        <v>8932</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>238.0886907801636</v>
+        <v>251.1965771959166</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>45.69987713160841</v>
+        <v>50.0767099336147</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>17.57347584250184</v>
+        <v>15.78666141569403</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.2900147090196607</v>
+        <v>0.5416365423366842</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.2309925474581738</v>
+        <v>-0.2785236677727967</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>8240</v>
+        <v>9955</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>232.3304375492121</v>
+        <v>249.3905025040084</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>56.9</v>
+        <v>26.95</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>41.06026707733121</v>
+        <v>41.56393126250083</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17.6570474291032</v>
+        <v>22.08637766232699</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.3784004600914926</v>
+        <v>0.8478093000344159</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.4066624415175961</v>
+        <v>-0.0069721954082601</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>9911</v>
+        <v>8423</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>216.9158440768512</v>
+        <v>247.9677165388879</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>82.5</v>
+        <v>17.75</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>42.64636102650326</v>
+        <v>47.42774787046428</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>16.07948858734553</v>
+        <v>12.99136027841186</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.8937356373656931</v>
+        <v>0.585501965893761</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.06539592305870599</v>
+        <v>0.0138510445559368</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>9902</v>
+        <v>8183</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>212.8113607686478</v>
+        <v>247.8992485706265</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>13.7</v>
+        <v>32.55</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>44.25725229799259</v>
+        <v>51.57100202955373</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>13.84569900596543</v>
+        <v>13.67037259938761</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.5057807995197909</v>
+        <v>0.5956788085759926</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-5.747267480316065e-06</v>
+        <v>0.1811238874444771</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8092</v>
+        <v>8940</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>209.0827545295187</v>
+        <v>247.5093482338217</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>14.7</v>
+        <v>17</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>35.97105866685007</v>
+        <v>52.42296538395827</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>19.45577697317589</v>
+        <v>12.85198973149178</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.2037525174983434</v>
+        <v>0.7557164579987778</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.2597082669107117</v>
+        <v>0.06767875877061461</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8367</v>
+        <v>8462</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>207.747594201945</v>
+        <v>245.9832095376832</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>40.3</v>
+        <v>139</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>35.23857489894685</v>
+        <v>42.51033602022531</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>23.83195336594492</v>
+        <v>15.82974213584188</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.6535506356687394</v>
+        <v>1.583061511248226</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,11 +5764,11 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.0496854182753221</v>
+        <v>0.3308498866567189</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -5785,7 +5785,7 @@
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>207.4651697464145</v>
+        <v>237.4651697464146</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>52.1</v>
@@ -5799,10 +5799,10 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.55510303206482</v>
+        <v>49.55510315163959</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>19.46036409332492</v>
+        <v>19.4603640654907</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.3891821979964652</v>
@@ -5817,7 +5817,7 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.2203320990626896</v>
+        <v>-0.2203320989386727</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
@@ -5827,21 +5827,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>8440</v>
+        <v>9802</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>206.9511362125146</v>
+        <v>227.7390701495025</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>22.25</v>
+        <v>77.2</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>46.57976618411514</v>
+        <v>46.96766917961627</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.9944180828951</v>
+        <v>13.33484427533565</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.298240744037497</v>
+        <v>0.6582024689620007</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1181668638823019</v>
+        <v>-0.0619540624215436</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>9802</v>
+        <v>8440</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>197.7390701495027</v>
+        <v>226.9511362125146</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>77.2</v>
+        <v>22.25</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>46.9676693937968</v>
+        <v>46.57976618411514</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>13.33484417692599</v>
+        <v>13.9944180828951</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.6582024689620007</v>
+        <v>0.298240744037497</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.0619540629366768</v>
+        <v>-0.1181668638155249</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8059</v>
+        <v>8467</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>189.485409864732</v>
+        <v>217.158736050271</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>17.1</v>
+        <v>125.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>34.97044088662547</v>
+        <v>50.39347791263204</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>16.75376403182905</v>
+        <v>18.22085328219561</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.204088037145369</v>
+        <v>0.3948463225838985</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.2228921455129768</v>
+        <v>0.8959223630906665</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8467</v>
+        <v>8092</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>187.158736050271</v>
+        <v>209.0827545295187</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>125.5</v>
+        <v>14.7</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>50.39347794159831</v>
+        <v>35.97105868580729</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>18.2208531913415</v>
+        <v>19.45577705274811</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.3948463225838985</v>
+        <v>0.2037525174983434</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.8959223616597001</v>
+        <v>-0.2597082667485355</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8213</v>
+        <v>8367</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>184.5993430971008</v>
+        <v>207.747594201945</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>37.2</v>
+        <v>40.3</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>50.68635028072362</v>
+        <v>35.23857473046098</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>14.72141450407407</v>
+        <v>23.83195337517425</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.5074716210899242</v>
+        <v>0.6535506356687394</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0779741551209816</v>
+        <v>0.0496854183611842</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8404</v>
+        <v>9911</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>183.7820562688517</v>
+        <v>196.9158440768512</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>16.65</v>
+        <v>82.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>42.67447556165112</v>
+        <v>42.64636110919275</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14.18604176713618</v>
+        <v>16.07948863689387</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.5387953767228029</v>
+        <v>0.8937356373656931</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.0211521221448092</v>
+        <v>-0.06539592305870599</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8482</v>
+        <v>8222</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>173.8876742049017</v>
+        <v>192.890713060268</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>0</v>
+        <v>35.25</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>29.74884497210465</v>
+        <v>47.63250889797202</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>8.089197832410317</v>
+        <v>13.03958204821956</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0</v>
+        <v>0.4790099303238202</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-2.400675066722908</v>
+        <v>-0.07548376100023629</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8431</v>
+        <v>8059</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>155.3131014945473</v>
+        <v>189.485409864732</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>57.6</v>
+        <v>17.1</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>54.27990389092297</v>
+        <v>34.97044048596004</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>16.80451560276355</v>
+        <v>16.75376427859515</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.19642007569765</v>
+        <v>1.204088037145369</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.8006526449583271</v>
+        <v>-0.2228921450455283</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8084</v>
+        <v>8404</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>150.0312462888161</v>
+        <v>163.7820562688517</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>47.2</v>
+        <v>16.65</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>54.21631385118466</v>
+        <v>42.67447553398669</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>16.53087807426387</v>
+        <v>14.18604178841848</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.124527112112848</v>
+        <v>0.5387953767228029</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.238397534722087</v>
+        <v>-0.0211521220971098</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8085</v>
+        <v>8084</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>148.4628191657874</v>
+        <v>150.0312462888161</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>12.9</v>
+        <v>47.2</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>49.73967303971504</v>
+        <v>54.21631385118466</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>22.71263574057617</v>
+        <v>16.53087812877231</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.484434350461888</v>
+        <v>1.124527112112848</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0060491272257336</v>
+        <v>-0.2383975347316248</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8410</v>
+        <v>8085</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>森田</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>135.4027957870001</v>
+        <v>148.4628191657874</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>32.9</v>
+        <v>12.9</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>34.80289444047996</v>
+        <v>49.73967293071676</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>21.36411293018368</v>
+        <v>22.71263587359793</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.2402795787000142</v>
+        <v>0.484434350461888</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,7 +6400,7 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1272162658038914</v>
+        <v>-0.006049126863225</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
@@ -6410,21 +6410,21 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8222</v>
+        <v>8213</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>132.8907130602777</v>
+        <v>144.5993430971007</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>35.25</v>
+        <v>37.2</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>47.63250876788579</v>
+        <v>50.68635029928281</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>13.03958186403358</v>
+        <v>14.72141451389095</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.4790099303238202</v>
+        <v>0.5074716210899242</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.07548376092391849</v>
+        <v>-0.07797415510190329</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>8463</v>
+        <v>8410</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>森田</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>116.2754991178575</v>
+        <v>135.4027957870001</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>21.3</v>
+        <v>32.9</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>37.70080958126318</v>
+        <v>34.80289435536275</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.24679518662265</v>
+        <v>21.36411328860463</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.144130862861971</v>
+        <v>0.2402795787000142</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,62 +6506,168 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.008693393150002801</v>
+        <v>-0.1272162657084909</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
+        <v>8482</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>商億-KY</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>133.8876742049231</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>29.74884496616488</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>8.089197887538361</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-2.400675066627514</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>8463</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>潤泰材</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>116.2754991178574</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>37.7008095242328</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>13.24679533244739</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>1.144130862861971</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>0.008693393226318701</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
         <v>8171</v>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>天宇</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="n">
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>109.2712660088053</v>
       </c>
-      <c r="E115" s="2" t="n">
+      <c r="E117" s="2" t="n">
         <v>21.55</v>
       </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>40.36568744595269</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>18.45980422930276</v>
-      </c>
-      <c r="J115" s="2" t="n">
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>40.36568753246303</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>18.45980423753382</v>
+      </c>
+      <c r="J117" s="2" t="n">
         <v>0.6430719708929121</v>
       </c>
-      <c r="K115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" s="2" t="n">
-        <v>-0.309592507248364</v>
-      </c>
-      <c r="O115" s="2" t="inlineStr">
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.3095925074200782</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>

--- a/output/full_scan/batch_seq0_2026-06-18.xlsx
+++ b/output/full_scan/batch_seq0_2026-06-18.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O117"/>
+  <dimension ref="A1:O116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1155.853310953276</v>
+        <v>1195.853310953276</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>1590</v>
@@ -739,21 +739,21 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>8086</v>
+        <v>8215</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>宏捷科</t>
+          <t>明基材</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1054.360297485652</v>
+        <v>1073.569112560659</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>166</v>
+        <v>31.15</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,49 +764,49 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>57.71111548486585</v>
+        <v>56.81011835213402</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>21.56960171470994</v>
+        <v>27.04284492152312</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.164992444713737</v>
+        <v>1.639649367515072</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>0.1422459219353504</v>
+        <v>0.0326497432797794</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>8358</v>
+        <v>8086</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>宏捷科</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1041.009352392484</v>
+        <v>1054.360297485652</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>700</v>
+        <v>166</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>69.04403229048192</v>
+        <v>57.71111548486585</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>23.06894061513817</v>
+        <v>21.56960171470994</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.7056367516551425</v>
+        <v>1.164992444713737</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>2.076261091978374</v>
+        <v>0.1422459219353504</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, bb_squeeze_breakout, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>8121</v>
+        <v>8358</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>越峰</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1037.262126417864</v>
+        <v>1041.009352392484</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>53.4</v>
+        <v>700</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>75.93609080874364</v>
+        <v>69.04403229048192</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>46.70069252349768</v>
+        <v>23.06894061513817</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.544987984983442</v>
+        <v>0.7056367516551425</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.8737442589074651</v>
+        <v>2.076261091978374</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, adx_trending, stronger_than_market, bb_squeeze_breakout, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8215</v>
+        <v>8121</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>明基材</t>
+          <t>越峰</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1033.569112560659</v>
+        <v>1037.262126417864</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>31.15</v>
+        <v>53.4</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,49 +923,49 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>56.81011835213402</v>
+        <v>75.93609080874364</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>27.04284492152312</v>
+        <v>46.70069252349768</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>1.639649367515072</v>
+        <v>1.544987984983442</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0.0326497432797794</v>
+        <v>0.8737442589074651</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>8162</v>
+        <v>8163</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>微矽電子-創</t>
+          <t>達方</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>898.5046576435245</v>
+        <v>937.1515826794952</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>44.95</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>63.85196161387863</v>
+        <v>71.74573519855514</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>40.24633442339601</v>
+        <v>49.79088880869254</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.567442051946094</v>
+        <v>1.171170220501482</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.4335849669893434</v>
+        <v>0.08844939460700189</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8163</v>
+        <v>8438</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>達方</t>
+          <t>昶昕</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>897.1515826794953</v>
+        <v>930.5228465530488</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>44.95</v>
+        <v>92.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>71.74573519855514</v>
+        <v>58.67902818406253</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>49.79088880869254</v>
+        <v>14.57775227466842</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.171170220501482</v>
+        <v>2.959531275522715</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,11 +1047,11 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.08844939460700189</v>
+        <v>0.5272493879090294</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>896.702351686249</v>
+        <v>916.702351686249</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>215</v>
@@ -1110,21 +1110,21 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>8438</v>
+        <v>8162</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>昶昕</t>
+          <t>微矽電子-創</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>890.5228465530489</v>
+        <v>898.5046576435245</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>92.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>58.67902818406253</v>
+        <v>63.85196161387863</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>14.57775227466842</v>
+        <v>40.24633442339601</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>2.959531275522715</v>
+        <v>1.567442051946094</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.5272493879090294</v>
+        <v>-0.4335849669893434</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>8476</v>
+        <v>8096</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>台境*</t>
+          <t>擎亞</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>888.1208831555517</v>
+        <v>875.5250652683885</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>21.75</v>
+        <v>155.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>84.31001297108764</v>
+        <v>72.18532653945576</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45.00316505244118</v>
+        <v>44.18588691588744</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>2.912088315555169</v>
+        <v>0.7203246007847947</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.5541364431437922</v>
+        <v>1.807926965731887</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>8096</v>
+        <v>8476</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>擎亞</t>
+          <t>台境*</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>875.5250652683885</v>
+        <v>858.1208831555517</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>155.5</v>
+        <v>21.75</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>72.18532653945576</v>
+        <v>84.31001297108764</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>44.18588691588744</v>
+        <v>45.00316505244118</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7203246007847947</v>
+        <v>2.912088315555169</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.807926965731887</v>
+        <v>0.5541364431437922</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>8071</v>
+        <v>8926</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>能率網通</t>
+          <t>台汽電</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>815.3018019305124</v>
+        <v>835.4604029481216</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>29.4</v>
+        <v>79</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,49 +1294,49 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>72.67611105911736</v>
+        <v>70.25998962481813</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>44.8860879633117</v>
+        <v>52.1627035734376</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.9847190895920004</v>
+        <v>0.8690289882885064</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.7530224316757033</v>
+        <v>0.1949277299780902</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>8926</v>
+        <v>8071</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>台汽電</t>
+          <t>能率網通</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>795.4604029481216</v>
+        <v>815.3018019305124</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>79</v>
+        <v>29.4</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,49 +1347,49 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>70.25998962481813</v>
+        <v>72.67611105911736</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>52.1627035734376</v>
+        <v>44.8860879633117</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.8690289882885064</v>
+        <v>0.9847190895920004</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.1949277299780902</v>
+        <v>0.7530224316757033</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>8454</v>
+        <v>8112</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>富邦媒</t>
+          <t>至上</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>775.5899539744237</v>
+        <v>772.4444267459938</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>341</v>
+        <v>98.2</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,29 +1400,29 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>60.04521210663605</v>
+        <v>61.75508233411573</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>53.07203140060524</v>
+        <v>25.8623405089959</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.4129375977969646</v>
+        <v>0.421772935862368</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-3.73556959725768</v>
+        <v>0.5103956454779883</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1534,21 +1534,21 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>8112</v>
+        <v>8072</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>至上</t>
+          <t>陞泰</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>732.4444267459938</v>
+        <v>739.7429042208328</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>98.2</v>
+        <v>29.4</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,49 +1559,49 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>61.75508233411573</v>
+        <v>56.53291229429286</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>25.8623405089959</v>
+        <v>22.71628386793744</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.421772935862368</v>
+        <v>0.8253136942312305</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>2</v>
       </c>
       <c r="L21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>0.5103956454779883</v>
+        <v>0.01813126120341</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>8076</v>
+        <v>8488</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>伍豐</t>
+          <t>吉源-KY</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>731.6368520244017</v>
+        <v>734.3576534660657</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>25.75</v>
+        <v>10.55</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>51.69424156179807</v>
+        <v>54.31968271960501</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>22.431747942232</v>
+        <v>11.52070081506104</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5250873403966899</v>
+        <v>0.4213806284477214</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.1767854190157202</v>
+        <v>0.050370102272073</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>8105</v>
+        <v>8076</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>凌巨</t>
+          <t>伍豐</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>718.7211697479768</v>
+        <v>731.6368520244017</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>21.9</v>
+        <v>25.75</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>65.19188567018112</v>
+        <v>51.69424156179807</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>41.19884809914242</v>
+        <v>22.431747942232</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.7588550714363653</v>
+        <v>0.5250873403966899</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>1</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.0227908851512006</v>
+        <v>-0.1767854190157202</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>8104</v>
+        <v>8499</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>錸寶</t>
+          <t>鼎炫-KY</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>710.187417986814</v>
+        <v>731.5452454546102</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>42.35</v>
+        <v>304</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>61.36984925690612</v>
+        <v>55.3472782183686</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>31.24790243999222</v>
+        <v>14.77989475140978</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.43601893816944</v>
+        <v>0.4035730410363002</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-0.061119653482994</v>
+        <v>0.2193070184356582</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8155</v>
+        <v>8105</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>博智</t>
+          <t>凌巨</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>704.8409076963212</v>
+        <v>718.7211697479768</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>404.5</v>
+        <v>21.9</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>56.62878197545385</v>
+        <v>65.19188567018112</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>19.42216355662317</v>
+        <v>41.19884809914242</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.7286666136586196</v>
+        <v>0.7588550714363653</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>2.389014179137372</v>
+        <v>0.0227908851512006</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8072</v>
+        <v>8473</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>陞泰</t>
+          <t>山林水</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>699.7429042208328</v>
+        <v>715.1747735264522</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>29.4</v>
+        <v>50</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>56.53291229429286</v>
+        <v>57.93937361535146</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>22.71628386793744</v>
+        <v>37.58338584790121</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.8253136942312305</v>
+        <v>0.3216518492864711</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.01813126120341</v>
+        <v>-0.7074883681156581</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>8473</v>
+        <v>8131</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>山林水</t>
+          <t>福懋科</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>695.1747735264522</v>
+        <v>709.5485995398493</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>50</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>57.93937361535146</v>
+        <v>60.21988201490265</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>37.58338584790121</v>
+        <v>16.13060111251273</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.3216518492864711</v>
+        <v>0.7203650281217829</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.7074883681156581</v>
+        <v>0.5138690387225906</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>8488</v>
+        <v>8155</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>吉源-KY</t>
+          <t>博智</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>694.3576534660657</v>
+        <v>704.8409076963212</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>10.55</v>
+        <v>404.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>54.31968271960501</v>
+        <v>56.62878197545385</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>11.52070081506104</v>
+        <v>19.42216355662317</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4213806284477214</v>
+        <v>0.7286666136586196</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.050370102272073</v>
+        <v>2.389014179137372</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8499</v>
+        <v>8110</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>鼎炫-KY</t>
+          <t>華東</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>691.5452454546102</v>
+        <v>693.265532549499</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>304</v>
+        <v>59.2</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>55.3472782183686</v>
+        <v>57.57288957913019</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>14.77989475140978</v>
+        <v>18.18224149505588</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4035730410363002</v>
+        <v>0.5303929645891792</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.2193070184356582</v>
+        <v>-0.0187531580316782</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>9912</v>
+        <v>8104</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>偉聯</t>
+          <t>錸寶</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>675.4825753324391</v>
+        <v>680.187417986814</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>12.65</v>
+        <v>42.35</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>56.77164012606635</v>
+        <v>61.36984925690612</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>21.77269587606584</v>
+        <v>31.24790243999222</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.1482575332439052</v>
+        <v>1.43601893816944</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,11 +2054,11 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.0108650058121316</v>
+        <v>-0.061119653482994</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2117,21 +2117,21 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8131</v>
+        <v>8390</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>福懋科</t>
+          <t>金益鼎</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>669.5485995398493</v>
+        <v>655.3455214206044</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>114</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>60.21988201490265</v>
+        <v>49.45085486065919</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>16.13060111251273</v>
+        <v>27.54129967618764</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.7203650281217829</v>
+        <v>0.8232000378977669</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>1</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.5138690387225906</v>
+        <v>-1.924104158559102</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>8390</v>
+        <v>8070</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>金益鼎</t>
+          <t>長華*</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>655.3455214206044</v>
+        <v>649.7017946632876</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>114</v>
+        <v>55</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>49.45085486065919</v>
+        <v>52.80344353169039</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>27.54129967618764</v>
+        <v>28.91457806866354</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.8232000378977669</v>
+        <v>0.3794917228330856</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-1.924104158559102</v>
+        <v>-0.6298633157039246</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8110</v>
+        <v>8374</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>華東</t>
+          <t>羅昇</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>653.265532549499</v>
+        <v>649.6788244174722</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>59.2</v>
+        <v>91</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>57.57288957913019</v>
+        <v>45.73648665440056</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>18.18224149505588</v>
+        <v>19.24014436228724</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.5303929645891792</v>
+        <v>0.2500614123425246</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,11 +2266,11 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-0.0187531580316782</v>
+        <v>-1.637911620008658</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2382,21 +2382,21 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8299</v>
+        <v>9912</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>群聯</t>
+          <t>偉聯</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>643.1243941611358</v>
+        <v>645.4825753324391</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2530</v>
+        <v>12.65</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,49 +2407,49 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>55.41740483822416</v>
+        <v>56.77164012606635</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>15.53698698524009</v>
+        <v>21.77269587606584</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.078945723721084</v>
+        <v>0.1482575332439052</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-21.54329255527637</v>
+        <v>0.0108650058121316</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8472</v>
+        <v>8299</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>夠麻吉</t>
+          <t>群聯</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>623.7277693227371</v>
+        <v>643.1243941611358</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>85.5</v>
+        <v>2530</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,49 +2460,49 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>56.09315923728956</v>
+        <v>55.41740483822416</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>28.48304235708011</v>
+        <v>15.53698698524009</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.0446880676429455</v>
+        <v>1.078945723721084</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-0.4838855884646884</v>
+        <v>-21.54329255527637</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>8383</v>
+        <v>8472</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>千附</t>
+          <t>夠麻吉</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>614.3378558329428</v>
+        <v>623.7277693227371</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>60.4</v>
+        <v>85.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>52.90682818116999</v>
+        <v>56.09315923728956</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15.85208672734539</v>
+        <v>28.48304235708011</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5014785425891116</v>
+        <v>0.0446880676429455</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>0.0001553530481321</v>
+        <v>-0.4838855884646884</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>8182</v>
+        <v>8383</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>加高</t>
+          <t>千附</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>613.2018474242929</v>
+        <v>614.3378558329428</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>51</v>
+        <v>60.4</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>58.75510056928735</v>
+        <v>52.90682818116999</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>28.27668792031824</v>
+        <v>15.85208672734539</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.3842023107047386</v>
+        <v>0.5014785425891116</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1623615238471472</v>
+        <v>0.0001553530481321</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>8070</v>
+        <v>8182</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>長華*</t>
+          <t>加高</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>609.7017946632876</v>
+        <v>613.2018474242929</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>52.80344353169039</v>
+        <v>58.75510056928735</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>28.91457806866354</v>
+        <v>28.27668792031824</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.3794917228330856</v>
+        <v>0.3842023107047386</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-0.6298633157039246</v>
+        <v>0.1623615238471472</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8374</v>
+        <v>8341</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>羅昇</t>
+          <t>日友</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>609.6788244174722</v>
+        <v>609.6675098134273</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>91</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45.73648665440056</v>
+        <v>58.95113406624979</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>19.24014436228724</v>
+        <v>27.58821510398439</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.2500614123425246</v>
+        <v>0.541528718514066</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-1.637911620008658</v>
+        <v>0.1033912333850146</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>8049</v>
+        <v>8481</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>晶采</t>
+          <t>政伸</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>597.7001100879544</v>
+        <v>598.332906863063</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>27.7</v>
+        <v>42.1</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>62.15242187792689</v>
+        <v>65.03013428144452</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>25.21061429508586</v>
+        <v>28.08286115400882</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.784328461850071</v>
+        <v>0.2287099038011074</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0676234060627154</v>
+        <v>0.1472931744900086</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>9136</v>
+        <v>8049</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>巨騰-DR</t>
+          <t>晶采</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>596.3712942171848</v>
+        <v>597.7001100879544</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>16.7</v>
+        <v>27.7</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>68.12523699545898</v>
+        <v>62.15242187792689</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>53.27705616779544</v>
+        <v>25.21061429508586</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3973425721198888</v>
+        <v>0.784328461850071</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.07650017157432649</v>
+        <v>0.0676234060627154</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>8097</v>
+        <v>9136</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>常珵</t>
+          <t>巨騰-DR</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>593.3863436447973</v>
+        <v>596.3712942171848</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>60.3</v>
+        <v>16.7</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>61.94978168801831</v>
+        <v>68.12523699545898</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>26.30944128685361</v>
+        <v>53.27705616779544</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.104663461656446</v>
+        <v>0.3973425721198888</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-0.08639489316300381</v>
+        <v>-0.07650017157432649</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>8069</v>
+        <v>8097</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>元太</t>
+          <t>常珵</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>582.1069887125407</v>
+        <v>593.3863436447973</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>204</v>
+        <v>60.3</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>51.17272891764441</v>
+        <v>61.94978168801831</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>24.2564967733027</v>
+        <v>26.30944128685361</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.279254106786174</v>
+        <v>1.104663461656446</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-3.774413579516368</v>
+        <v>-0.08639489316300381</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>9907</v>
+        <v>8069</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>統一實</t>
+          <t>元太</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>579.0165349655372</v>
+        <v>582.1069887125407</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>16.7</v>
+        <v>204</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>52.22988369399163</v>
+        <v>51.17272891764441</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>21.66726423292999</v>
+        <v>24.2564967733027</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.34951109035133</v>
+        <v>1.279254106786174</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.080413073099921</v>
+        <v>-3.774413579516368</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8341</v>
+        <v>8210</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>日友</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>569.6675098134273</v>
+        <v>578.4915512369838</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>1365</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>58.95113406624979</v>
+        <v>49.67300081800688</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>27.58821510398439</v>
+        <v>21.67862955376237</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.541528718514066</v>
+        <v>0.6617032259710059</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.1033912333850146</v>
+        <v>-17.72274853072158</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8102</v>
+        <v>9905</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>傑霖科技</t>
+          <t>大華</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>564.053417284901</v>
+        <v>577.2249845343975</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>71.90000000000001</v>
+        <v>21.05</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>53.33748621701348</v>
+        <v>57.77401140328696</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>11.82006646968299</v>
+        <v>17.58795026071824</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.6692022450081282</v>
+        <v>0.4720299394802166</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.7240692413123728</v>
+        <v>0.0641032332594579</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>8481</v>
+        <v>8464</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>政伸</t>
+          <t>億豐</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>558.332906863063</v>
+        <v>565.8962450110483</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>42.1</v>
+        <v>358</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,49 +3096,49 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>65.03013428144452</v>
+        <v>65.60310648095518</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>28.08286115400882</v>
+        <v>19.41685786728148</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.2287099038011074</v>
+        <v>1.232676659989646</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L50" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M50" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.1472931744900086</v>
+        <v>4.441399040436155</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8464</v>
+        <v>8102</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>億豐</t>
+          <t>傑霖科技</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>545.8962450110483</v>
+        <v>564.053417284901</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>358</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,49 +3149,49 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>65.60310648095518</v>
+        <v>53.33748621701348</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>19.41685786728148</v>
+        <v>11.82006646968299</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.232676659989646</v>
+        <v>0.6692022450081282</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M51" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>4.441399040436155</v>
+        <v>-0.7240692413123728</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>8289</v>
+        <v>9907</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>泰藝</t>
+          <t>統一實</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>541.4865908102521</v>
+        <v>549.0165349655372</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>53.51604533190066</v>
+        <v>52.22988369399163</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>31.68555592769697</v>
+        <v>21.66726423292999</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.404624734127143</v>
+        <v>2.34951109035133</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-1.136857436777838</v>
+        <v>0.080413073099921</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8210</v>
+        <v>8150</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>538.4915512369838</v>
+        <v>548.8430734199715</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>1365</v>
+        <v>104</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,49 +3255,49 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>49.67300081800688</v>
+        <v>60.01922406754734</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>21.67862955376237</v>
+        <v>27.32463813529739</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.6617032259710059</v>
+        <v>1.24397190127226</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-17.72274853072158</v>
+        <v>-0.3721165364437979</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>9905</v>
+        <v>8289</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>大華</t>
+          <t>泰藝</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>537.2249845343975</v>
+        <v>541.4865908102521</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>21.05</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>57.77401140328696</v>
+        <v>53.51604533190066</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>17.58795026071824</v>
+        <v>31.68555592769697</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4720299394802166</v>
+        <v>0.404624734127143</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0641032332594579</v>
+        <v>-1.136857436777838</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8150</v>
+        <v>8201</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>無敵</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>508.8430734199715</v>
+        <v>519.3119614310266</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>104</v>
+        <v>13.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,29 +3361,29 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>60.01922406754734</v>
+        <v>52.29169882303583</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>27.32463813529739</v>
+        <v>22.90330873716831</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.24397190127226</v>
+        <v>0.3861157022261797</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.3721165364437979</v>
+        <v>-0.0158929566417384</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -3495,21 +3495,21 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8201</v>
+        <v>9906</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>無敵</t>
+          <t>欣巴巴</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>479.3119614310266</v>
+        <v>490.5188776804987</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>13.5</v>
+        <v>46.8</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.29169882303583</v>
+        <v>66.85193063403479</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>22.90330873716831</v>
+        <v>41.40916464164901</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3861157022261797</v>
+        <v>2.191740628696065</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.0158929566417384</v>
+        <v>0.8050964845447268</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>8080</v>
+        <v>8271</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>永利聯合</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>470.6087851783257</v>
+        <v>477.5958194479642</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>28.8</v>
+        <v>211</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>56.45154460523543</v>
+        <v>45.63758887204092</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>43.37176839127427</v>
+        <v>21.06666723098323</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7756517776826294</v>
+        <v>0.4745126093154982</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.0891562017286243</v>
+        <v>-3.291086552932189</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, cci_momentum</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>9110</v>
+        <v>8080</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>越南控-DR</t>
+          <t>永利聯合</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>463.7111404797045</v>
+        <v>470.6087851783257</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>3.4</v>
+        <v>28.8</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>54.38827536821917</v>
+        <v>56.45154460523543</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15.74909254953022</v>
+        <v>43.37176839127427</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.2778971617596257</v>
+        <v>0.7756517776826294</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.0104481036359067</v>
+        <v>0.0891562017286243</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>9930</v>
+        <v>9110</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>中聯資源</t>
+          <t>越南控-DR</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>462.3042774755675</v>
+        <v>463.7111404797045</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>70</v>
+        <v>3.4</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>58.46715913726457</v>
+        <v>54.38827536821917</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>12.44044185185889</v>
+        <v>15.74909254953022</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.169870024537477</v>
+        <v>0.2778971617596257</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.1533665392640847</v>
+        <v>-0.0104481036359067</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>9103</v>
+        <v>9930</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>美德醫療-DR</t>
+          <t>中聯資源</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>461.5604128376081</v>
+        <v>462.3042774755675</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>5.33</v>
+        <v>70</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>48.38557725352536</v>
+        <v>58.46715913726457</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>32.99696616510596</v>
+        <v>12.44044185185889</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.3714204211342013</v>
+        <v>1.169870024537477</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0644255513587223</v>
+        <v>0.1533665392640847</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>9906</v>
+        <v>9103</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>欣巴巴</t>
+          <t>美德醫療-DR</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>450.5188776804988</v>
+        <v>461.5604128376081</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>46.8</v>
+        <v>5.33</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>66.85193063403479</v>
+        <v>48.38557725352536</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>41.40916464164901</v>
+        <v>32.99696616510596</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2.191740628696065</v>
+        <v>0.3714204211342013</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.8050964845447268</v>
+        <v>-0.0644255513587223</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>8087</v>
+        <v>9910</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>華鎂鑫</t>
+          <t>豐泰</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>448.7492886899026</v>
+        <v>457.3920881368412</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>33.1</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>44.12416580371332</v>
+        <v>43.81768797397033</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.25952175859864</v>
+        <v>25.52107577369674</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.625635842633647</v>
+        <v>0.5864932777212982</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-0.23235002093175</v>
+        <v>-0.8750232240499938</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>8271</v>
+        <v>8087</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>華鎂鑫</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>437.5958194479642</v>
+        <v>448.7492886899026</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>211</v>
+        <v>33.1</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45.63758887204092</v>
+        <v>44.12416580371332</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>21.06666723098323</v>
+        <v>20.25952175859864</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.4745126093154982</v>
+        <v>0.625635842633647</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-3.291086552932189</v>
+        <v>-0.23235002093175</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>9910</v>
+        <v>8411</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>豐泰</t>
+          <t>福貞-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>417.3920881368412</v>
+        <v>429.4175481065753</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>12.15</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>43.81768797397033</v>
+        <v>49.91804091976477</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>25.52107577369674</v>
+        <v>33.77147256005432</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5864932777212982</v>
+        <v>1.687056878824431</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.8750232240499938</v>
+        <v>0.01054904063613</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8101</v>
+        <v>8442</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>華冠</t>
+          <t>威宏-KY</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>404.0027008741864</v>
+        <v>418.0301115522864</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>14.45</v>
+        <v>40.3</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>49.4994945389498</v>
+        <v>35.98476082437912</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15.59200879353696</v>
+        <v>22.1417566843635</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.2949415259518292</v>
+        <v>0.6260510736652275</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.154532186358273</v>
+        <v>0.4217338447914149</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>8176</v>
+        <v>9904</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>智捷</t>
+          <t>寶成</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>402.5398038362733</v>
+        <v>407.6726002816658</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>10.15</v>
+        <v>26.15</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46.88977771623104</v>
+        <v>48.14128497683792</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>9.021694678918497</v>
+        <v>17.83460861250862</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.245876290072259</v>
+        <v>2.106641881407974</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0044568676957452</v>
+        <v>0.058975238870303</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>8068</v>
+        <v>8176</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>全達</t>
+          <t>智捷</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>392.7506539284531</v>
+        <v>402.5398038362733</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>19.2</v>
+        <v>10.15</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>41.29453027294502</v>
+        <v>46.88977771623104</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>23.74262922136042</v>
+        <v>9.021694678918497</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.92859899366724</v>
+        <v>1.245876290072259</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.0490773109040287</v>
+        <v>0.0044568676957452</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>8411</v>
+        <v>8068</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>福貞-KY</t>
+          <t>全達</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>389.4175481065753</v>
+        <v>392.7506539284531</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>12.15</v>
+        <v>19.2</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.91804091976477</v>
+        <v>41.29453027294502</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>33.77147256005432</v>
+        <v>23.74262922136042</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.687056878824431</v>
+        <v>0.92859899366724</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.01054904063613</v>
+        <v>0.0490773109040287</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>9904</v>
+        <v>8054</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>寶成</t>
+          <t>安國</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>387.6726002816658</v>
+        <v>374.9125939734548</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>26.15</v>
+        <v>103.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>48.14128497683792</v>
+        <v>51.41739109336533</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>17.83460861250862</v>
+        <v>10.66746599368151</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>2.106641881407974</v>
+        <v>0.8530098015440434</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.058975238870303</v>
+        <v>-0.0109047733709579</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>8442</v>
+        <v>8101</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>威宏-KY</t>
+          <t>華冠</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>378.0301115522864</v>
+        <v>374.0027008741864</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>40.3</v>
+        <v>14.45</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>35.98476082437912</v>
+        <v>49.4994945389498</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>22.1417566843635</v>
+        <v>15.59200879353696</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.6260510736652275</v>
+        <v>0.2949415259518292</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.4217338447914149</v>
+        <v>-0.154532186358273</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>8054</v>
+        <v>8477</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>安國</t>
+          <t>創業家</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>374.9125939734548</v>
+        <v>372.5606681884926</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>103.5</v>
+        <v>17.2</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>51.41739109336533</v>
+        <v>49.13203001979202</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>10.66746599368151</v>
+        <v>28.20344555008747</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.8530098015440434</v>
+        <v>0.35685727326736</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>2</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-0.0109047733709579</v>
+        <v>-0.4065303894924257</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8114</v>
+        <v>8067</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>振樺電</t>
+          <t>志旭</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>374.233634195929</v>
+        <v>368.6342266126773</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>212</v>
+        <v>12.8</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.86859040910159</v>
+        <v>50.82317182677548</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>27.71518865929537</v>
+        <v>6.61555089611803</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.4735362483682783</v>
+        <v>0.6358510214776845</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-4.299485125008794</v>
+        <v>-0.1641368224779111</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>8477</v>
+        <v>8103</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>創業家</t>
+          <t>瀚荃</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>372.5606681884926</v>
+        <v>367.0146493282012</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>17.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>49.13203001979202</v>
+        <v>44.18854536222097</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>28.20344555008747</v>
+        <v>20.4517868018715</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.35685727326736</v>
+        <v>0.5409881363708172</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>2</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.4065303894924257</v>
+        <v>-0.7162891852622097</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>8067</v>
+        <v>8455</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>志旭</t>
+          <t>大拓-KY</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>368.6342266126773</v>
+        <v>366.535021036419</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>12.8</v>
+        <v>31.1</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>50.82317182677548</v>
+        <v>45.40372605236342</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>6.61555089611803</v>
+        <v>23.05434328144319</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.6358510214776845</v>
+        <v>0.1955059621391223</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1641368224779111</v>
+        <v>-1.091089417054512</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8455</v>
+        <v>8431</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>大拓-KY</t>
+          <t>匯鑽科</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>366.535021036419</v>
+        <v>355.3131014945473</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>31.1</v>
+        <v>57.6</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45.40372605236342</v>
+        <v>54.27990389585754</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>23.05434328144319</v>
+        <v>16.80451562805866</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.1955059621391223</v>
+        <v>1.19642007569765</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-1.091089417054512</v>
+        <v>0.8006526449964846</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>8431</v>
+        <v>9908</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>匯鑽科</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>355.3131014945473</v>
+        <v>351.2236966339877</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>57.6</v>
+        <v>29.55</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>54.27990389585754</v>
+        <v>54.89931306089676</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>16.80451562805866</v>
+        <v>15.44949202565718</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.19642007569765</v>
+        <v>1.359640313823974</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.8006526449964846</v>
+        <v>0.0529898624164991</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>9902</v>
+        <v>8487</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>台火</t>
+          <t>愛爾達-創</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>352.811360768634</v>
+        <v>348.0886907801635</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>13.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,16 +4633,16 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>44.25725224951844</v>
+        <v>45.69987712678162</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>13.84569900861393</v>
+        <v>17.57347580463314</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5057807995197909</v>
+        <v>0.2900147090196607</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-5.747257940474926e-06</v>
+        <v>-0.2309925473627782</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>9908</v>
+        <v>8422</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>可寧衛*</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>351.2236966339877</v>
+        <v>347.6263480424821</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>29.55</v>
+        <v>28.1</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>54.89931306089676</v>
+        <v>49.7386024874543</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>15.44949202565718</v>
+        <v>16.26696395599885</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.359640313823974</v>
+        <v>0.5636579756162637</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.0529898624164991</v>
+        <v>0.0565524569541111</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>8487</v>
+        <v>8114</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>愛爾達-創</t>
+          <t>振樺電</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>348.0886907801635</v>
+        <v>344.233634195929</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>212</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45.69987712678162</v>
+        <v>45.86859040910159</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>17.57347580463314</v>
+        <v>27.71518865929537</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.2900147090196607</v>
+        <v>0.4735362483682783</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.2309925473627782</v>
+        <v>-4.299485125008794</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8466</v>
+        <v>8240</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>美吉吉-KY</t>
+          <t>華宏</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>342.8717668937186</v>
+        <v>342.3304375492121</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>15.55</v>
+        <v>56.9</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45.87086468382787</v>
+        <v>41.06026707528156</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>21.00218212608815</v>
+        <v>17.6570474420099</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.586492457580184</v>
+        <v>0.3784004600914926</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0244693464355625</v>
+        <v>-0.4066624414126591</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>8240</v>
+        <v>8074</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>華宏</t>
+          <t>鉅橡</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>342.3304375492121</v>
+        <v>339.8744013306601</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>56.9</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>41.06026707528156</v>
+        <v>49.44624212724676</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>17.6570474420099</v>
+        <v>10.79600427039511</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.3784004600914926</v>
+        <v>0.6524551145598754</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.4066624414126591</v>
+        <v>0.09693375857894999</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>8074</v>
+        <v>8227</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>鉅橡</t>
+          <t>巨有科技</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>339.8744013306601</v>
+        <v>337.4274005798313</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>73.90000000000001</v>
+        <v>184.5</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>49.44624212724676</v>
+        <v>46.33647509632365</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>10.79600427039511</v>
+        <v>24.41225788821432</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.6524551145598754</v>
+        <v>0.4795257708521274</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.09693375857894999</v>
+        <v>-4.061197610538376</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>8227</v>
+        <v>8089</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>巨有科技</t>
+          <t>康全電訊</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>337.4274005798313</v>
+        <v>334.0010156160555</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>184.5</v>
+        <v>21.15</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>46.33647509632365</v>
+        <v>51.64787532633137</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>24.41225788821432</v>
+        <v>33.79497216679643</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4795257708521274</v>
+        <v>0.99562590604665</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-4.061197610538376</v>
+        <v>0.1105617847145457</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8089</v>
+        <v>8111</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>康全電訊</t>
+          <t>立碁</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>334.0010156160555</v>
+        <v>330.6251297313991</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>21.15</v>
+        <v>56.2</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>51.64787532633137</v>
+        <v>37.31698985574555</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>33.79497216679643</v>
+        <v>27.19021227969117</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.99562590604665</v>
+        <v>0.7916411375919936</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.1105617847145457</v>
+        <v>-0.5533431235268038</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>8111</v>
+        <v>9902</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>立碁</t>
+          <t>台火</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>330.6251297313991</v>
+        <v>322.811360768634</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>56.2</v>
+        <v>13.7</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>37.31698985574555</v>
+        <v>44.25725224951844</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>27.19021227969117</v>
+        <v>13.84569900861393</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.7916411375919936</v>
+        <v>0.5057807995197909</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.5533431235268038</v>
+        <v>-5.747257940474926e-06</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8103</v>
+        <v>8429</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>瀚荃</t>
+          <t>金麗-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>327.0146493282012</v>
+        <v>317.044486780294</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>97.09999999999999</v>
+        <v>6.51</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>44.18854536222097</v>
+        <v>49.23215618114228</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>20.4517868018715</v>
+        <v>26.60722660423146</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5409881363708172</v>
+        <v>1.380266615582537</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>2</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.7162891852622097</v>
+        <v>0.0180581745643384</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>8429</v>
+        <v>8466</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>金麗-KY</t>
+          <t>美吉吉-KY</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>317.044486780294</v>
+        <v>312.8717668937186</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>6.51</v>
+        <v>15.55</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>49.23215618114228</v>
+        <v>45.87086468382787</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>26.60722660423146</v>
+        <v>21.00218212608815</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.380266615582537</v>
+        <v>0.586492457580184</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0180581745643384</v>
+        <v>0.0244693464355625</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>8422</v>
+        <v>8234</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>可寧衛*</t>
+          <t>新漢</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>307.6263480424821</v>
+        <v>304.7133424084689</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>28.1</v>
+        <v>63.6</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>49.7386024874543</v>
+        <v>43.30283782207498</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>16.26696395599885</v>
+        <v>18.06138796917998</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5636579756162637</v>
+        <v>0.3231887694475174</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0565524569541111</v>
+        <v>-0.6990391735133873</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>8234</v>
+        <v>8147</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>新漢</t>
+          <t>正淩</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>304.7133424084689</v>
+        <v>294.7928650992018</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>63.6</v>
+        <v>146.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>43.30283782207498</v>
+        <v>39.87389930504136</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>18.06138796917998</v>
+        <v>21.57334451226114</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.3231887694475174</v>
+        <v>0.4033979836180008</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.6990391735133873</v>
+        <v>-2.172759522725013</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8443</v>
+        <v>8462</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>阿瘦</t>
+          <t>柏文</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>296.7481694139776</v>
+        <v>285.9832095376831</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>11.4</v>
+        <v>139</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>48.28717664246225</v>
+        <v>42.51033602022531</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>56.43766512446177</v>
+        <v>15.82974213584188</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4656928902496394</v>
+        <v>1.583061511248226</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0305161088348983</v>
+        <v>0.3308498866567189</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8147</v>
+        <v>8443</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>正淩</t>
+          <t>阿瘦</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>294.7928650992018</v>
+        <v>266.7481694139776</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>146.5</v>
+        <v>11.4</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>39.87389930504136</v>
+        <v>48.28717664246225</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>21.57334451226114</v>
+        <v>56.43766512446177</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4033979836180008</v>
+        <v>0.4656928902496394</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-2.172759522725013</v>
+        <v>0.0305161088348983</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>8478</v>
+        <v>8932</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>東哥遊艇</t>
+          <t>智通*</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>272.7858263219994</v>
+        <v>251.1965771959166</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>151</v>
+        <v>100</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>41.65355115099919</v>
+        <v>50.0767099336147</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.53001859418741</v>
+        <v>15.78666141569403</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.7646322489312642</v>
+        <v>0.5416365423366842</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.3240151441903944</v>
+        <v>-0.2785236677727967</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>8932</v>
+        <v>9955</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>智通*</t>
+          <t>佳龍</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>251.1965771959166</v>
+        <v>249.3905025040084</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>100</v>
+        <v>26.95</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>50.0767099336147</v>
+        <v>41.56393126250083</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15.78666141569403</v>
+        <v>22.08637766232699</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.5416365423366842</v>
+        <v>0.8478093000344159</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.2785236677727967</v>
+        <v>-0.0069721954082601</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>9955</v>
+        <v>8423</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>佳龍</t>
+          <t>保綠-KY</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>249.3905025040084</v>
+        <v>247.9677165388879</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>26.95</v>
+        <v>17.75</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>41.56393126250083</v>
+        <v>47.42774787046428</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>22.08637766232699</v>
+        <v>12.99136027841186</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.8478093000344159</v>
+        <v>0.585501965893761</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.0069721954082601</v>
+        <v>0.0138510445559368</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8423</v>
+        <v>8183</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>保綠-KY</t>
+          <t>精星</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>247.9677165388879</v>
+        <v>247.8992485706265</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>17.75</v>
+        <v>32.55</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>47.42774787046428</v>
+        <v>51.57100202955373</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>12.99136027841186</v>
+        <v>13.67037259938761</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.585501965893761</v>
+        <v>0.5956788085759926</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.0138510445559368</v>
+        <v>0.1811238874444771</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>8183</v>
+        <v>8940</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>精星</t>
+          <t>新天地</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>247.8992485706265</v>
+        <v>247.5093482338217</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>32.55</v>
+        <v>17</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>51.57100202955373</v>
+        <v>52.42296538395827</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>13.67037259938761</v>
+        <v>12.85198973149178</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.5956788085759926</v>
+        <v>0.7557164579987778</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.1811238874444771</v>
+        <v>0.06767875877061461</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8940</v>
+        <v>8478</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>新天地</t>
+          <t>東哥遊艇</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>247.5093482338217</v>
+        <v>242.7858263219995</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>17</v>
+        <v>151</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>52.42296538395827</v>
+        <v>41.65355115099919</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>12.85198973149178</v>
+        <v>16.53001859418741</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.7557164579987778</v>
+        <v>0.7646322489312642</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.06767875877061461</v>
+        <v>-0.3240151441903944</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8462</v>
+        <v>8440</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>綠電</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>245.9832095376832</v>
+        <v>226.9511362125146</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>139</v>
+        <v>22.25</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>42.51033602022531</v>
+        <v>46.57976618411514</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>15.82974213584188</v>
+        <v>13.9944180828951</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.583061511248226</v>
+        <v>0.298240744037497</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.3308498866567189</v>
+        <v>-0.1181668638155249</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>8249</v>
+        <v>9911</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>菱光</t>
+          <t>櫻花</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>237.4651697464146</v>
+        <v>216.9158440768512</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>52.1</v>
+        <v>82.5</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.55510315163959</v>
+        <v>42.64636110919275</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>19.4603640654907</v>
+        <v>16.07948863689387</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.3891821979964652</v>
+        <v>0.8937356373656931</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.2203320989386727</v>
+        <v>-0.06539592305870599</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>9802</v>
+        <v>8092</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>鈺齊-KY</t>
+          <t>建暐</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>227.7390701495025</v>
+        <v>209.0827545295187</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>77.2</v>
+        <v>14.7</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>46.96766917961627</v>
+        <v>35.97105868580729</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.33484427533565</v>
+        <v>19.45577705274811</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6582024689620007</v>
+        <v>0.2037525174983434</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0619540624215436</v>
+        <v>-0.2597082667485355</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8440</v>
+        <v>8367</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>綠電</t>
+          <t>建新國際</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>226.9511362125146</v>
+        <v>207.747594201945</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>22.25</v>
+        <v>40.3</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>46.57976618411514</v>
+        <v>35.23857473046098</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>13.9944180828951</v>
+        <v>23.83195337517425</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.298240744037497</v>
+        <v>0.6535506356687394</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.1181668638155249</v>
+        <v>0.0496854183611842</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8467</v>
+        <v>8249</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>波力-KY</t>
+          <t>菱光</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>217.158736050271</v>
+        <v>207.4651697464146</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>125.5</v>
+        <v>52.1</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>50.39347791263204</v>
+        <v>49.55510315163959</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>18.22085328219561</v>
+        <v>19.4603640654907</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3948463225838985</v>
+        <v>0.3891821979964652</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.8959223630906665</v>
+        <v>-0.2203320989386727</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>above_ema60, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>8092</v>
+        <v>9802</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>建暐</t>
+          <t>鈺齊-KY</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>209.0827545295187</v>
+        <v>197.7390701495025</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>14.7</v>
+        <v>77.2</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>35.97105868580729</v>
+        <v>46.96766917961627</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>19.45577705274811</v>
+        <v>13.33484427533565</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.2037525174983434</v>
+        <v>0.6582024689620007</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.2597082667485355</v>
+        <v>-0.0619540624215436</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>8367</v>
+        <v>8059</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>建新國際</t>
+          <t>凱碩</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>207.747594201945</v>
+        <v>189.485409864732</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>40.3</v>
+        <v>17.1</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>35.23857473046098</v>
+        <v>34.97044048596004</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>23.83195337517425</v>
+        <v>16.75376427859515</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6535506356687394</v>
+        <v>1.204088037145369</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0496854183611842</v>
+        <v>-0.2228921450455283</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>9911</v>
+        <v>8467</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>櫻花</t>
+          <t>波力-KY</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>196.9158440768512</v>
+        <v>187.158736050271</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>82.5</v>
+        <v>125.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>42.64636110919275</v>
+        <v>50.39347791263204</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>16.07948863689387</v>
+        <v>18.22085328219561</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.8937356373656931</v>
+        <v>0.3948463225838985</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.06539592305870599</v>
+        <v>0.8959223630906665</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>8222</v>
+        <v>8213</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>寶一</t>
+          <t>志超</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>192.890713060268</v>
+        <v>184.5993430971008</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>35.25</v>
+        <v>37.2</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>47.63250889797202</v>
+        <v>50.68635029928281</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>13.03958204821956</v>
+        <v>14.72141451389095</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4790099303238202</v>
+        <v>0.5074716210899242</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-0.07548376100023629</v>
+        <v>-0.07797415510190329</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>8059</v>
+        <v>8404</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>凱碩</t>
+          <t>百和興業-KY</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>189.485409864732</v>
+        <v>183.7820562688517</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>17.1</v>
+        <v>16.65</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>34.97044048596004</v>
+        <v>42.67447553398669</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>16.75376427859515</v>
+        <v>14.18604178841848</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.204088037145369</v>
+        <v>0.5387953767228029</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.2228921450455283</v>
+        <v>-0.0211521220971098</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8404</v>
+        <v>8482</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>百和興業-KY</t>
+          <t>商億-KY</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>163.7820562688517</v>
+        <v>173.8876742049231</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>16.65</v>
+        <v>0</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>42.67447553398669</v>
+        <v>29.74884496616488</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.18604178841848</v>
+        <v>8.089197887538361</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.5387953767228029</v>
+        <v>0</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0211521220971098</v>
+        <v>-2.400675066627514</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>8084</v>
+        <v>8222</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>巨虹</t>
+          <t>寶一</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>150.0312462888161</v>
+        <v>162.890713060268</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>47.2</v>
+        <v>35.25</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>54.21631385118466</v>
+        <v>47.63250889797202</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>16.53087812877231</v>
+        <v>13.03958204821956</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.124527112112848</v>
+        <v>0.4790099303238202</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.2383975347316248</v>
+        <v>-0.07548376100023629</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>8085</v>
+        <v>8084</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>福華</t>
+          <t>巨虹</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>148.4628191657874</v>
+        <v>150.0312462888161</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>12.9</v>
+        <v>47.2</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>49.73967293071676</v>
+        <v>54.21631385118466</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>22.71263587359793</v>
+        <v>16.53087812877231</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.484434350461888</v>
+        <v>1.124527112112848</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.006049126863225</v>
+        <v>-0.2383975347316248</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8213</v>
+        <v>8085</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>志超</t>
+          <t>福華</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>144.5993430971007</v>
+        <v>148.4628191657874</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>37.2</v>
+        <v>12.9</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>50.68635029928281</v>
+        <v>49.73967293071676</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>14.72141451389095</v>
+        <v>22.71263587359793</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5074716210899242</v>
+        <v>0.484434350461888</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,11 +6453,11 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.07797415510190329</v>
+        <v>-0.006049126863225</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
@@ -6516,21 +6516,21 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8482</v>
+        <v>8463</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>商億-KY</t>
+          <t>潤泰材</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>133.8876742049231</v>
+        <v>116.2754991178574</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>0</v>
+        <v>21.3</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>29.74884496616488</v>
+        <v>37.7008095242328</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>8.089197887538361</v>
+        <v>13.24679533244739</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0</v>
+        <v>1.144130862861971</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,7 +6559,7 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-2.400675066627514</v>
+        <v>0.008693393226318701</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
@@ -6569,21 +6569,21 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8463</v>
+        <v>8171</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>潤泰材</t>
+          <t>天宇</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>116.2754991178574</v>
+        <v>109.2712660088053</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>21.3</v>
+        <v>21.55</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>37.7008095242328</v>
+        <v>40.36568753246303</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>13.24679533244739</v>
+        <v>18.45980423753382</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.144130862861971</v>
+        <v>0.6430719708929121</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,62 +6612,9 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.008693393226318701</v>
+        <v>-0.3095925074200782</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
-        <is>
-          <t>market_above_ma60, avoid_chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="n">
-        <v>8171</v>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>天宇</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>109.2712660088053</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>21.55</v>
-      </c>
-      <c r="F117" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="G117" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>40.36568753246303</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>18.45980423753382</v>
-      </c>
-      <c r="J117" s="2" t="n">
-        <v>0.6430719708929121</v>
-      </c>
-      <c r="K117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L117" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N117" s="2" t="n">
-        <v>-0.3095925074200782</v>
-      </c>
-      <c r="O117" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
